--- a/templates/Шаблон_спецификации_РД_KKS.xlsx
+++ b/templates/Шаблон_спецификации_РД_KKS.xlsx
@@ -9,6 +9,7 @@
   </bookViews>
   <sheets>
     <sheet name="Спецификация" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="ГОСТы" sheetId="2" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">Спецификация!$A$2:$J$2</definedName>
@@ -66,7 +67,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
   <si>
     <t xml:space="preserve">Поз. по спецификации</t>
   </si>
@@ -96,6 +97,15 @@
   </si>
   <si>
     <t xml:space="preserve">Примечание</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ГОСТ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Наименовние</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Область применения</t>
   </si>
 </sst>
 </file>
@@ -227,51 +237,51 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="5" fillId="0" borderId="0" xfId="21" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="5" fillId="0" borderId="0" xfId="21" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="5" fillId="0" borderId="0" xfId="21" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="5" fillId="0" borderId="0" xfId="21" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="21" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="21" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="6" fillId="0" borderId="0" xfId="21" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="6" fillId="0" borderId="0" xfId="21" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="21" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="168" fontId="5" fillId="0" borderId="0" xfId="21" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="21" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="5" fillId="0" borderId="0" xfId="21" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="5" fillId="2" borderId="1" xfId="21" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="5" fillId="2" borderId="1" xfId="21" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="true"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="5" fillId="0" borderId="1" xfId="21" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="5" fillId="0" borderId="1" xfId="21" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="true"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="5" fillId="0" borderId="1" xfId="21" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="5" fillId="0" borderId="1" xfId="21" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="true"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="5" fillId="0" borderId="1" xfId="21" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="5" fillId="0" borderId="1" xfId="21" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="21" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="21" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="true"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="21" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -605,7 +615,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" s="12" customFormat="true" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="8"/>
       <c r="B3" s="8"/>
       <c r="C3" s="9"/>
@@ -616,7 +626,7 @@
       <c r="H3" s="11"/>
       <c r="I3" s="11"/>
       <c r="J3" s="10"/>
-      <c r="K3" s="0"/>
+      <c r="K3" s="12"/>
     </row>
   </sheetData>
   <autoFilter ref="A2:J2"/>
@@ -629,4 +639,54 @@
   </headerFooter>
   <drawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:C14"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="12" width="35.94"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="12" width="83.31"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="12" width="67.01"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="8"/>
+      <c r="B2" s="9"/>
+      <c r="C2" s="9"/>
+    </row>
+    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,Обычный"&amp;12&amp;Kffffff&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Обычный"&amp;12&amp;KffffffСтраница &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
 </file>
--- a/templates/Шаблон_спецификации_РД_KKS.xlsx
+++ b/templates/Шаблон_спецификации_РД_KKS.xlsx
@@ -102,7 +102,7 @@
     <t xml:space="preserve">ГОСТ</t>
   </si>
   <si>
-    <t xml:space="preserve">Наименовние</t>
+    <t xml:space="preserve">Наименование</t>
   </si>
   <si>
     <t xml:space="preserve">Область применения</t>

--- a/templates/Шаблон_спецификации_РД_KKS.xlsx
+++ b/templates/Шаблон_спецификации_РД_KKS.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Спецификация" sheetId="1" state="visible" r:id="rId3"/>

--- a/templates/Шаблон_спецификации_РД_KKS.xlsx
+++ b/templates/Шаблон_спецификации_РД_KKS.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="Спецификация" sheetId="1" state="visible" r:id="rId3"/>
